--- a/shared_store/ground_truth.xlsx
+++ b/shared_store/ground_truth.xlsx
@@ -460,59 +460,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>550482</v>
+        <v>652538</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Av. Belgrano 1827, Tigre</t>
+          <t>Av. Rivadavia 4561, Moron</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>563</v>
+        <v>757.8</v>
       </c>
       <c r="E2" t="n">
-        <v>64</v>
+        <v>156</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="G2" t="n">
-        <v>2020</v>
+        <v>1974</v>
       </c>
       <c r="H2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>239789</v>
+        <v>302018</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Av. Rivadavia 4267, Tigre</t>
+          <t>Av. Belgrano 807, La Matanza</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1276.4</v>
+        <v>563.6</v>
       </c>
       <c r="E3" t="n">
-        <v>118</v>
+        <v>350</v>
       </c>
       <c r="F3" t="n">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="G3" t="n">
-        <v>1993</v>
+        <v>1964</v>
       </c>
       <c r="H3" t="n">
         <v>14</v>
@@ -520,239 +520,239 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>699807</v>
+        <v>948454</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Calle Moreno 2043, Moron</t>
+          <t>Calle Sarmiento 1628, Tigre</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1054.8</v>
+        <v>957</v>
       </c>
       <c r="E4" t="n">
-        <v>189</v>
+        <v>115</v>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>851040</v>
+        <v>653798</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Av. Corrientes 4978, Vicente Lopez</t>
+          <t>Av. Rivadavia 2351, Moron</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>627.8</v>
+        <v>1178.6</v>
       </c>
       <c r="E5" t="n">
-        <v>162</v>
+        <v>317</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G5" t="n">
-        <v>2019</v>
+        <v>2001</v>
       </c>
       <c r="H5" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>41376</v>
+        <v>455390</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Av. Corrientes 2450, Vicente Lopez</t>
+          <t>Av. Belgrano 2448, Quilmes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1118.7</v>
+        <v>835.4</v>
       </c>
       <c r="E6" t="n">
-        <v>206</v>
+        <v>28</v>
       </c>
       <c r="F6" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="G6" t="n">
-        <v>2015</v>
+        <v>1959</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>549312</v>
+        <v>945063</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Av. Belgrano 4209, San Isidro</t>
+          <t>Calle Mitre 3999, Moron</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1272.6</v>
+        <v>766.8</v>
       </c>
       <c r="E7" t="n">
-        <v>34</v>
+        <v>207</v>
       </c>
       <c r="F7" t="n">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="G7" t="n">
-        <v>2013</v>
+        <v>1975</v>
       </c>
       <c r="H7" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>713065</v>
+        <v>360881</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Av. Libertador 4547, Lomas de Zamora</t>
+          <t>Calle Moreno 2410, Tigre</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>217</v>
+        <v>637.6</v>
       </c>
       <c r="E8" t="n">
-        <v>94</v>
+        <v>250</v>
       </c>
       <c r="F8" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>1969</v>
+        <v>1986</v>
       </c>
       <c r="H8" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>923643</v>
+        <v>264401</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Av. Libertador 3660, Vicente Lopez</t>
+          <t>Av. Corrientes 1050, San Isidro</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>127.3</v>
+        <v>966.8</v>
       </c>
       <c r="E9" t="n">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="F9" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="G9" t="n">
-        <v>1957</v>
+        <v>2017</v>
       </c>
       <c r="H9" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>74654</v>
+        <v>253626</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Av. Corrientes 3353, Lomas de Zamora</t>
+          <t>Av. Corrientes 579, San Isidro</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>177.3</v>
+        <v>426.1</v>
       </c>
       <c r="E10" t="n">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G10" t="n">
-        <v>1981</v>
+        <v>2009</v>
       </c>
       <c r="H10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>814659</v>
+        <v>178230</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Calle Moreno 4346, San Isidro</t>
+          <t>Av. Libertador 969, Quilmes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1345.2</v>
+        <v>296.9</v>
       </c>
       <c r="E11" t="n">
-        <v>178</v>
+        <v>351</v>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="G11" t="n">
-        <v>2005</v>
+        <v>1991</v>
       </c>
       <c r="H11" t="n">
         <v>12</v>
@@ -760,301 +760,301 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>267990</v>
+        <v>533864</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Calle Mitre 864, Tigre</t>
+          <t>Calle Sarmiento 3038, Moron</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>487.2</v>
+        <v>384.9</v>
       </c>
       <c r="E12" t="n">
-        <v>98</v>
+        <v>330</v>
       </c>
       <c r="F12" t="n">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>1983</v>
+        <v>2009</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>371851</v>
+        <v>432930</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Calle Sarmiento 3081, La Matanza</t>
+          <t>Calle Sarmiento 2795, San Isidro</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>521.3</v>
+        <v>905</v>
       </c>
       <c r="E13" t="n">
-        <v>189</v>
+        <v>87</v>
       </c>
       <c r="F13" t="n">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="G13" t="n">
-        <v>2004</v>
+        <v>1984</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>768904</v>
+        <v>844599</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Av. Libertador 3663, Moron</t>
+          <t>Av. Belgrano 2822, Moron</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>186.1</v>
+        <v>559.3</v>
       </c>
       <c r="E14" t="n">
-        <v>319</v>
+        <v>211</v>
       </c>
       <c r="F14" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G14" t="n">
-        <v>1961</v>
+        <v>2020</v>
       </c>
       <c r="H14" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>982505</v>
+        <v>842699</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Av. Rivadavia 2352, Moron</t>
+          <t>Av. Libertador 1967, Quilmes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1347.8</v>
+        <v>230.8</v>
       </c>
       <c r="E15" t="n">
-        <v>38</v>
+        <v>176</v>
       </c>
       <c r="F15" t="n">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="G15" t="n">
-        <v>1974</v>
+        <v>1981</v>
       </c>
       <c r="H15" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>256587</v>
+        <v>942366</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Av. Libertador 4150, San Miguel</t>
+          <t>Calle Mitre 2273, Quilmes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1283.5</v>
+        <v>1065.1</v>
       </c>
       <c r="E16" t="n">
-        <v>307</v>
+        <v>115</v>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="G16" t="n">
-        <v>1975</v>
+        <v>2017</v>
       </c>
       <c r="H16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>584445</v>
+        <v>925478</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Av. San Martin 1671, Lomas de Zamora</t>
+          <t>Av. Rivadavia 3506, Moron</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>446.7</v>
+        <v>427.1</v>
       </c>
       <c r="E17" t="n">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="F17" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="G17" t="n">
-        <v>1985</v>
+        <v>2009</v>
       </c>
       <c r="H17" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>307022</v>
+        <v>936921</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Av. Rivadavia 2651, Quilmes</t>
+          <t>Av. Corrientes 3337, Tigre</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1323</v>
+        <v>745</v>
       </c>
       <c r="E18" t="n">
-        <v>259</v>
+        <v>177</v>
       </c>
       <c r="F18" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G18" t="n">
-        <v>1970</v>
+        <v>1960</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>754155</v>
+        <v>780783</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Av. Libertador 1491, Quilmes</t>
+          <t>Calle Moreno 2309, Quilmes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>152.3</v>
+        <v>1219.5</v>
       </c>
       <c r="E19" t="n">
-        <v>88</v>
+        <v>350</v>
       </c>
       <c r="F19" t="n">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="G19" t="n">
-        <v>1983</v>
+        <v>2014</v>
       </c>
       <c r="H19" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>800814</v>
+        <v>917609</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Av. Corrientes 3583, La Matanza</t>
+          <t>Av. San Martin 185, Lomas de Zamora</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1180.9</v>
+        <v>236</v>
       </c>
       <c r="E20" t="n">
-        <v>311</v>
+        <v>151</v>
       </c>
       <c r="F20" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="G20" t="n">
-        <v>1982</v>
+        <v>1966</v>
       </c>
       <c r="H20" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>42251</t>
+          <t>292001</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Av. Libertador 1136, Vicente Lopez</t>
+          <t>Av. Libertador 1672, Vicente Lopez</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1221.4</v>
+        <v>1209.2</v>
       </c>
       <c r="E21" t="n">
-        <v>302</v>
+        <v>323</v>
       </c>
       <c r="F21" t="n">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="G21" t="n">
-        <v>1985</v>
+        <v>1958</v>
       </c>
       <c r="H21" t="n">
         <v>13</v>
